--- a/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, un orage arrive. Diane a peur. Son ventre se serre. Elle ne reste pas seule avec la peur. Elle va raconter à papa ou maman. Elle dit : papa, j'ai peur. Le tonnerre. Papa l'écoute. Maman arrive. Diane raconte aussi à maman. Papa dit : merci de raconter. Ce qui fait peur se raconte à papa ou maman. Ils restent près. Diane respire.</t>
+          <t>Le soir, un orage arrive. Diane a peur. Son ventre se serre. Elle ne reste pas seule avec la peur. Elle va raconter à papa ou maman. Papa, j'ai peur. Le tonnerre. Papa l'écoute. Maman arrive. Diane raconte aussi à maman. Merci de raconter. Ce qui fait peur se raconte à papa ou maman. Ils restent près. Diane respire.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, un orage arrive. Diane a peur. Son ventre se serre. Elle ne reste pas seule avec la peur. Elle va raconter à papa ou maman.
+narrateur|Papa, j'ai peur.
+narrateur|Le tonnerre. Papa l'écoute. Maman arrive. Diane raconte aussi à maman.
+papa|Merci de raconter. Ce qui fait peur se raconte à papa ou maman. Ils restent près.
+narrateur|Diane respire.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Diane a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Diane a eu peur. Elle a raconté à papa et maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose un coussin. Diane s'allonge.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Diane respire.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Diane a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Diane a eu peur. Elle a raconté à papa et maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Maman pose un coussin. Diane s'allonge.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diane raconte sa peur de l'orage</t>
+          <t>Chouchou raconte l'orage</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La gouttière chante la pluie. Chouchou a peur du tonnerre. Elle raconte à papa et à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, un orage arrive. Diane a peur. Son ventre se serre. Elle ne reste pas seule avec la peur. Elle va raconter à papa ou maman. Papa, j'ai peur. Le tonnerre. Papa l'écoute. Maman arrive. Diane raconte aussi à maman. Merci de raconter. Ce qui fait peur se raconte à papa ou maman. Ils restent près. Diane respire.</t>
+          <t>La gouttière chante la pluie. L'eau tape un rythme tout doux. Puis le rythme devient plus fort. La lampe du salon clignote un peu. La soupe sent le poireau. Un doudou attend sur le canapé. Sa couture est un peu rêche. Chouchou, le doudou t'attend. La soupe va être prête. En ce moment, un orage arrive. Le tonnerre roule au loin. Puis il arrive plus près. Chouchou sent son ventre. Le ventre se serre. Chouchou a peur. Elle ne reste pas seule. Elle prend le doudou. Elle marche vers papa. Papa, j'ai peur. Le tonnerre. Mon ventre est serré. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le doudou aussi ? Oui, Chouchou. Bravo. Maman arrive avec un torchon. J'ai entendu le tonnerre. Chouchou marche aussi vers maman. Maman, j'ai peur. J'ai raconté à papa. Merci de raconter. Ce qui fait peur se raconte. On va raconter à papa ou maman. On reste près. Tu as fait du bon travail. Je respire. Oui. On respire ensemble. La gouttière chante encore. La lampe reste allumée. Le doudou est contre la joue. Un autre tonnerre passe plus loin. Il est moins fort. Oui. On est là. Bravo, Chouchou. Tu as raconté. La soupe fume dans la cuisine. Chouchou serre le doudou. Le doudou sent le lit. Tu as raconté tout de suite. Oui. Je ne suis pas restée seule. C'est ça. On va raconter à papa ou maman. Papa pose une main chaude. Maman s'assoit tout près. La fenêtre est un peu embuée. Une goutte glisse sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, un orage arrive. Diane a peur. Son ventre se serre. Elle ne reste pas seule avec la peur. Elle va raconter à papa ou maman.
-narrateur|Papa, j'ai peur.
-narrateur|Le tonnerre. Papa l'écoute. Maman arrive. Diane raconte aussi à maman.
-papa|Merci de raconter. Ce qui fait peur se raconte à papa ou maman. Ils restent près.
-narrateur|Diane respire.</t>
+          <t>narrateur|La gouttière chante la pluie.
+narrateur|L'eau tape un rythme tout doux.
+narrateur|Puis le rythme devient plus fort.
+narrateur|La lampe du salon clignote un peu.
+narrateur|La soupe sent le poireau.
+narrateur|Un doudou attend sur le canapé.
+narrateur|Sa couture est un peu rêche.
+maman|Chouchou, le doudou t'attend.
+papa|La soupe va être prête.
+narrateur|En ce moment, un orage arrive.
+narrateur|Le tonnerre roule au loin.
+narrateur|Puis il arrive plus près.
+narrateur|Chouchou sent son ventre.
+narrateur|Le ventre se serre.
+narrateur|Chouchou a peur.
+narrateur|Elle ne reste pas seule.
+narrateur|Elle prend le doudou.
+narrateur|Elle marche vers papa.
+enfant-f|Papa, j'ai peur.
+enfant-f|Le tonnerre.
+enfant-f|Mon ventre est serré.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+papa|Je reste tout près.
+enfant-f|Le doudou aussi ?
+papa|Oui, Chouchou.
+papa|Bravo.
+narrateur|Maman arrive avec un torchon.
+maman|J'ai entendu le tonnerre.
+narrateur|Chouchou marche aussi vers maman.
+enfant-f|Maman, j'ai peur.
+enfant-f|J'ai raconté à papa.
+maman|Merci de raconter.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+maman|On reste près.
+papa|Tu as fait du bon travail.
+enfant-f|Je respire.
+maman|Oui.
+maman|On respire ensemble.
+narrateur|La gouttière chante encore.
+narrateur|La lampe reste allumée.
+narrateur|Le doudou est contre la joue.
+narrateur|Un autre tonnerre passe plus loin.
+enfant-f|Il est moins fort.
+papa|Oui.
+papa|On est là.
+maman|Bravo, Chouchou.
+maman|Tu as raconté.
+narrateur|La soupe fume dans la cuisine.
+narrateur|Chouchou serre le doudou.
+narrateur|Le doudou sent le lit.
+papa|Tu as raconté tout de suite.
+enfant-f|Oui.
+enfant-f|Je ne suis pas restée seule.
+maman|C'est ça.
+maman|On va raconter à papa ou maman.
+narrateur|Papa pose une main chaude.
+narrateur|Maman s'assoit tout près.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Une goutte glisse sur la vitre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Diane a peur. Que fait-elle ?</t>
+          <t>Chouchou a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1574,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Diane a peur. Que fait-elle ?</t>
+          <t>narrateur|Chouchou a peur.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Diane a eu peur. Elle a raconté à papa et maman.</t>
+          <t>Chouchou a eu peur. Elle a raconté à papa. Elle a raconté à maman. Tu as raconté l'orage ? Oui. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. Le doudou reste contre la joue. La gouttière chante plus doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1747,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Diane a eu peur. Elle a raconté à papa et maman.</t>
+          <t>narrateur|Chouchou a eu peur.
+narrateur|Elle a raconté à papa.
+narrateur|Elle a raconté à maman.
+papa|Tu as raconté l'orage ?
+enfant-f|Oui.
+maman|Bravo.
+maman|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+narrateur|Le doudou reste contre la joue.
+narrateur|La gouttière chante plus doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose un coussin. Diane s'allonge.</t>
+          <t>Maman pose un coussin. Chouchou s'allonge un peu. Le doudou est avec toi. La soupe attend encore. Le tonnerre est loin. Oui. Tu as raconté. C'est du bon travail. La lampe ne clignote plus. La pluie devient une chanson calme. On reste encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1920,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose un coussin. Diane s'allonge.</t>
+          <t>narrateur|Maman pose un coussin.
+narrateur|Chouchou s'allonge un peu.
+maman|Le doudou est avec toi.
+papa|La soupe attend encore.
+enfant-f|Le tonnerre est loin.
+maman|Oui.
+papa|Tu as raconté.
+papa|C'est du bon travail.
+narrateur|La lampe ne clignote plus.
+narrateur|La pluie devient une chanson calme.
+maman|On reste encore un peu.
+enfant-f|D'accord.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La gouttière a fini sa chanson. J'ai raconté. Bravo, Chouchou. On t'écoute. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2099,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La gouttière a fini sa chanson.
+enfant-f|J'ai raconté.
+papa|Bravo, Chouchou.
+maman|On t'écoute.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière chante la pluie. L'eau tape un rythme tout doux. Puis le rythme devient plus fort. La lampe du salon clignote un peu. La soupe sent le poireau. Un doudou attend sur le canapé. Sa couture est un peu rêche. Chouchou, le doudou t'attend. La soupe va être prête. En ce moment, un orage arrive. Le tonnerre roule au loin. Puis il arrive plus près. Chouchou sent son ventre. Le ventre se serre. Chouchou a peur. Elle ne reste pas seule. Elle prend le doudou. Elle marche vers papa. Papa, j'ai peur. Le tonnerre. Mon ventre est serré. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le doudou aussi ? Oui, Chouchou. Bravo. Maman arrive avec un torchon. J'ai entendu le tonnerre. Chouchou marche aussi vers maman. Maman, j'ai peur. J'ai raconté à papa. Merci de raconter. Ce qui fait peur se raconte. On va raconter à papa ou maman. On reste près. Tu as fait du bon travail. Je respire. Oui. On respire ensemble. La gouttière chante encore. La lampe reste allumée. Le doudou est contre la joue. Un autre tonnerre passe plus loin. Il est moins fort. Oui. On est là. Bravo, Chouchou. Tu as raconté. La soupe fume dans la cuisine. Chouchou serre le doudou. Le doudou sent le lit. Tu as raconté tout de suite. Oui. Je ne suis pas restée seule. C'est ça. On va raconter à papa ou maman. Papa pose une main chaude. Maman s'assoit tout près. La fenêtre est un peu embuée. Une goutte glisse sur la vitre.</t>
+          <t>La gouttière chante la pluie. L'eau tape un rythme tout doux. Puis le rythme devient plus fort. La lampe du salon clignote un peu. La soupe sent le poireau. Un doudou attend sur le canapé. Sa couture est un peu rêche. Chouchou, le doudou t'attend. La soupe va être prête. En ce moment, un orage arrive. Le tonnerre roule au loin. Puis il arrive plus près. Chouchou sent son ventre. Le ventre se serre. Chouchou a peur. Elle ne reste pas seule. Elle prend le doudou. Elle marche vers papa. Papa, j'ai peur. Le tonnerre. Mon ventre est serré. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le doudou aussi ? Oui, Chouchou. Bravo. Maman arrive avec un torchon. J'ai entendu le tonnerre. Chouchou marche aussi vers maman. Maman, j'ai peur. J'ai raconté à papa. Merci de raconter. Ce qui fait peur se raconte. On va raconter à papa ou maman. On reste près. Je respire. Oui. On respire ensemble. La gouttière chante encore. La lampe reste allumée. Le doudou est contre la joue. Un autre tonnerre passe plus loin. Il est moins fort. Oui. On est là. Bravo, Chouchou. Tu as raconté. La soupe fume dans la cuisine. Chouchou serre le doudou. Le doudou sent le lit. Tu as raconté tout de suite. Oui. Je ne suis pas restée seule. C'est ça. On va raconter à papa ou maman. Papa pose une main chaude. Maman s'assoit tout près. La fenêtre est un peu embuée. Une goutte glisse sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, un orage arrive. Diane a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Son ventre se serre. Elle ne reste pas seule avec la peur. Elle va raconter à papa ou maman. Elle dit : papa, j'ai peur. Le tonnerre. Papa l'écoute. Maman arrive. Diane raconte aussi à maman. Papa dit : merci de raconter. Ce qui fait peur se raconte à papa ou maman. Ils restent près. Diane respire.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière chante la pluie. L'eau tape un rythme tout doux. Puis le rythme devient plus fort. La lampe du salon clignote un peu. La soupe sent le poireau. Un doudou attend sur le canapé. Sa couture est un peu rêche. Chouchou, le doudou t'attend. La soupe va être prête. En ce moment, un orage arrive. Le tonnerre roule au loin. Puis il arrive plus près. Chouchou sent son ventre. Le ventre se serre. Chouchou a peur. Elle ne reste pas seule. Elle prend le doudou. Elle marche vers papa. Papa, j'ai peur. Le tonnerre. Mon ventre est serré. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le doudou aussi ? Oui, Chouchou. Bravo. Maman arrive avec un torchon. J'ai entendu le tonnerre. Chouchou marche aussi vers maman. Maman, j'ai peur. J'ai raconté à papa. Merci de raconter. Ce qui fait peur se raconte. On va raconter à papa ou maman. On reste près. Je respire. Oui. On respire ensemble. La gouttière chante encore. La lampe reste allumée. Le doudou est contre la joue. Un autre tonnerre passe plus loin. Il est moins fort. Oui. On est là. Bravo, Chouchou. Tu as raconté. La soupe fume dans la cuisine. Chouchou serre le doudou. Le doudou sent le lit. Tu as raconté tout de suite. Oui. Je ne suis pas restée seule. C'est ça. On va raconter à papa ou maman. Papa pose une main chaude. Maman s'assoit tout près. La fenêtre est un peu embuée. Une goutte glisse sur la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1362,7 +1362,6 @@
 maman|Ce qui fait peur se raconte.
 maman|On va raconter à papa ou maman.
 maman|On reste près.
-papa|Tu as fait du bon travail.
 enfant-f|Je respire.
 maman|Oui.
 maman|On respire ensemble.
@@ -1389,7 +1388,6 @@
 narrateur|Une goutte glisse sur la vitre.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1419,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1578,7 +1576,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1608,7 +1605,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane a eu &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Elle a raconté à papa et maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a eu peur. Elle a raconté à papa. Elle a raconté à maman. Tu as raconté l'orage ? Oui. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. Le doudou reste contre la joue. La gouttière chante plus doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,7 +1756,6 @@
 narrateur|La gouttière chante plus doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1784,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose un coussin. Chouchou s'allonge un peu. Le doudou est avec toi. La soupe attend encore. Le tonnerre est loin. Oui. Tu as raconté. C'est du bon travail. La lampe ne clignote plus. La pluie devient une chanson calme. On reste encore un peu. D'accord.</t>
+          <t>Maman pose un coussin. Chouchou s'allonge un peu. Le doudou est avec toi. La soupe attend encore. Le tonnerre est loin. Oui. Tu as raconté. La lampe ne clignote plus. La pluie devient une chanson calme. On reste encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman pose un coussin. Diane s'allonge.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose un coussin. Chouchou s'allonge un peu. Le doudou est avec toi. La soupe attend encore. Le tonnerre est loin. Oui. Tu as raconté. La lampe ne clignote plus. La pluie devient une chanson calme. On reste encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,14 +1923,12 @@
 enfant-f|Le tonnerre est loin.
 maman|Oui.
 papa|Tu as raconté.
-papa|C'est du bon travail.
 narrateur|La lampe ne clignote plus.
 narrateur|La pluie devient une chanson calme.
 maman|On reste encore un peu.
 enfant-f|D'accord.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La gouttière a fini sa chanson. J'ai raconté. Bravo, Chouchou. On t'écoute. L'histoire est finie.</t>
+          <t>La gouttière a fini sa chanson. J'ai raconté. Bravo, Chouchou. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière a fini sa chanson. J'ai raconté. Bravo, Chouchou. On t'écoute.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,11 +2096,9 @@
           <t>narrateur|La gouttière a fini sa chanson.
 enfant-f|J'ai raconté.
 papa|Bravo, Chouchou.
-maman|On t'écoute.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On t'écoute.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, orage, gouttière</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diane, papa, maman</t>
+          <t>Chouchou, papa, maman</t>
         </is>
       </c>
     </row>
